--- a/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
@@ -728,147 +728,143 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3513
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>335</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
+          <t xml:space="preserve">6839
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -884,147 +880,133 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">435
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">326
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1829
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">3266
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">780
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1040,49 +1022,50 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">48
+13
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">7226
 </t>
         </is>
       </c>
@@ -1094,91 +1077,91 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">596
+          <t xml:space="preserve">528
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -1197,145 +1180,129 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">324
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">486860108728
+171171808
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2261
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">732
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1354,144 +1321,145 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">2926
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">369
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>8121</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">548
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1281
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">742
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1510,137 +1478,140 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17836
+          <t xml:space="preserve">7835
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t xml:space="preserve">9629
+</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">824
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2785
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">92926
+</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">496
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1212
+</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">1357
+</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308 10
+          <t xml:space="preserve">22929
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">1328
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">1335
+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3891
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="n"/>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1659,140 +1630,145 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
+          <t xml:space="preserve">367
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1 36
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">8190
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">3888
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -1811,143 +1787,134 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4203
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t xml:space="preserve">3601
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">660
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">266
 </t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1887
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29332
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">563
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1295
-</t>
-        </is>
-      </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1966,143 +1933,147 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">22
+191
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9233
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">05
+711
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">22927
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -2121,145 +2092,144 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">2727
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2278,145 +2248,139 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">903
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">3607
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">2129
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="n"/>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -2435,145 +2399,145 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10060
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2591,76 +2555,79 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>53041</t>
+          <t xml:space="preserve">15992
+</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15242
+          <t xml:space="preserve">1529
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1317
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">368
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0289
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">019
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>097</t>
+          <t xml:space="preserve">1307
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2672,57 +2639,61 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">1219
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">361
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">617
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1763
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">1207
+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
+          <t xml:space="preserve">476
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2741,37 +2712,37 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3062
+          <t xml:space="preserve">34182
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2783,98 +2754,103 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>519</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">368
 </t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t xml:space="preserve">41
+</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1364
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">1453
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">337
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1425
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -2893,43 +2869,43 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">3686
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">2064
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2940,95 +2916,96 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">973
+</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">467
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t xml:space="preserve">1190
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -3047,19 +3024,18 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3071,120 +3047,122 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">662
+1254
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">2929
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3203,145 +3181,145 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">3659
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">2415
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">662
+1254
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t>514</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3359,145 +3337,143 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3575
+          <t xml:space="preserve">3408
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">2438
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">7250
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3513,19 +3489,19 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
+          <t xml:space="preserve">3993
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3189
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -3537,124 +3513,119 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">128
 </t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
+          <t xml:space="preserve">2126
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3670,142 +3641,147 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16101
+          <t xml:space="preserve">7326
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150519
+          <t xml:space="preserve">422999227
+1149 6
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">1324
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">563
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">4574532851
+12818
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1070
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1268
+</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">557
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1281
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">893
+</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">65
 </t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">984
-</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9728
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1227
-</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4940
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12529
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19116
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>39411</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3200
-</t>
-        </is>
-      </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18993
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">24
+78
 </t>
         </is>
       </c>
@@ -3824,125 +3800,146 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">575
+</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6018
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">311
 </t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11170
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="n"/>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">408
+</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">24
+78
 </t>
         </is>
       </c>
@@ -3961,125 +3958,142 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">067
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">235
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24127
+210
+</t>
+        </is>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>93</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n"/>
+          <t xml:space="preserve">779717
+1791818
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="n"/>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">7783
+181186
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>936</t>
+          <t xml:space="preserve">6541
+</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -4095,147 +4109,141 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">24
 </t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">44
 </t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">552
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">872
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -4251,147 +4259,144 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>329</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">399
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2861
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">08
+34
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -4407,37 +4412,36 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2823
+          <t xml:space="preserve">2907
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4449,31 +4453,31 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12201
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -4485,67 +4489,66 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4564,143 +4567,144 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1402
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">368
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">506
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">11
 </t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">853
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">286
 </t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">737
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4719,138 +4723,145 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13635
+          <t xml:space="preserve">0566
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15065
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4280
+</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">966
+</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">388
+</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1526
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1239
+</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">953
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">358
+</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1207
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">280
 </t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">569
-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1022
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4895
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1455
-</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>35451</t>
-        </is>
-      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>531</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4869,140 +4880,145 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
+          <t xml:space="preserve">2112
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">452
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111171
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">4826
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1409
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">3968
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">381
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">4417
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
@@ -5021,7 +5037,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
+          <t xml:space="preserve">3847
 </t>
         </is>
       </c>
@@ -5033,125 +5049,132 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n"/>
+          <t xml:space="preserve">785
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">439
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
@@ -5170,143 +5193,144 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">2423
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1600
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">46
 </t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1290
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2862 2
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">45
 </t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>854</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">834
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>9481</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5324,137 +5348,146 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">3116
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">226
+214
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n"/>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -5473,144 +5506,146 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844
+          <t xml:space="preserve">3534
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">754
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5628,144 +5663,144 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">4307
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">75
 </t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>283</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5783,139 +5818,146 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
+          <t xml:space="preserve">6937
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>00401</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t xml:space="preserve">1287
+</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">534
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>12034446</t>
+          <t xml:space="preserve">160
+</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>0444</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
+          <t xml:space="preserve">427
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
+          <t xml:space="preserve">537
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112879
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">792798
+11811
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3936
+          <t xml:space="preserve">3248
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">466
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">82745857727
+12119
 </t>
         </is>
       </c>
@@ -5934,134 +5976,145 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
+          <t xml:space="preserve">3387
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">356
+</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2410
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="n"/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3607
+</t>
+        </is>
+      </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1431
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">1368
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>465</t>
+          <t xml:space="preserve">1216
+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -6080,65 +6133,73 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">193
 </t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>5455</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n"/>
+          <t xml:space="preserve">269
+111
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">990
@@ -6147,66 +6208,67 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">632
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t xml:space="preserve">882
+</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6224,49 +6286,50 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">7924
+265
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">3192
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -6278,89 +6341,92 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">269
+111
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>988</t>
+          <t xml:space="preserve">978
+</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">705
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">71
+</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -6379,19 +6445,20 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
+          <t xml:space="preserve">7924
+265
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6403,120 +6470,120 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6535,19 +6602,19 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
+          <t xml:space="preserve">2363
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6559,114 +6626,122 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n"/>
+          <t xml:space="preserve">412
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>843</t>
+          <t xml:space="preserve">296
+</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6684,66 +6759,81 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>77797</t>
+          <t xml:space="preserve">722
+</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0196
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="n"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n"/>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n"/>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -6752,41 +6842,61 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8235
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3923
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -6805,87 +6915,145 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>77797</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
+          <t xml:space="preserve">3659
+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124612
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
+          <t xml:space="preserve">326
+</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621
+</t>
+        </is>
+      </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">462
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">841
+</t>
+        </is>
+      </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -6904,130 +7072,133 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">021
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7283
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7263
+</t>
+        </is>
+      </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">987
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">4500
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">3581
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1725
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -7041,94 +7212,144 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">376
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7283
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">411
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="n"/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n"/>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1442
+</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n"/>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
@@ -728,143 +728,147 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">3513
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">0975
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">1017
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">1330
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">112811
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6839
+          <t xml:space="preserve">1561
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+          <t xml:space="preserve">1743
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1100
+</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -880,133 +884,146 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">435
+          <t xml:space="preserve">2781
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n"/>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3266
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="n"/>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1022,146 +1039,139 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">123680
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-13
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">12063
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">14103
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7226
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">2213
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1251
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">2249
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1180,129 +1190,143 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">486860108728
-171171808
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
+          <t xml:space="preserve">4182
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">324
+</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">141
+</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">10113
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>461</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">19808
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">13119
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
+          <t xml:space="preserve">1595
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="n"/>
+          <t xml:space="preserve">1288
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">732
+</t>
+        </is>
+      </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -1321,145 +1345,145 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2926
+          <t xml:space="preserve">193680
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">369
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">2417
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2333
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1279
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">244
 </t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1478,140 +1502,85 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7835
-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1618
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9629
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1308
-</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">679
-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">171836
+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2785
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92926
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">4870
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">496
-</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">13715
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22929
+          <t xml:space="preserve">9080
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1328
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1335
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1901
+</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="n"/>
+      <c r="W9" s="3" t="n"/>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="n"/>
+          <t xml:space="preserve">10325
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13891
+</t>
+        </is>
+      </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -1630,145 +1599,140 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">367
+          <t xml:space="preserve">23567
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 36
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8190
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1787,134 +1751,144 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
-</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3601
+          <t xml:space="preserve">3933
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t xml:space="preserve">1266
+</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t xml:space="preserve">1187
+</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1711
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">1004
+</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">1563
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">1221
+</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">2295
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">26551
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="n"/>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">704
+</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1933,147 +1907,145 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">1418240
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-191
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">2201
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">12203
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-711
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">19580
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">1303
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22927
+          <t xml:space="preserve">7132
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -2092,144 +2064,140 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">12301
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">12291
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">2211
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1213
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1970
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">12291
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t xml:space="preserve">1130
+</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1264
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2248,139 +2216,144 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">18214
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3607
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2129
+          <t xml:space="preserve">10195
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">1801
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="n"/>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t xml:space="preserve">1286
+</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2399,144 +2372,144 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">3408
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>945</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">10080
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10060
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">1300
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1300
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2553,147 +2526,97 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15992
-</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1529
-</t>
-        </is>
-      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">997
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
+          <t xml:space="preserve">1545
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">368
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1307
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1864
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">14900
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1219
-</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">361
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1524
+</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">13310
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1207
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1763
+</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="n"/>
+      <c r="W16" s="3" t="n"/>
+      <c r="X16" s="3" t="n"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">476
+          <t xml:space="preserve">13861
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">423
 </t>
         </is>
       </c>
@@ -2712,43 +2635,43 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34182
+          <t xml:space="preserve">3062
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -2758,99 +2681,89 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">368
-</t>
-        </is>
-      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1364
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">1662
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1453
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
-</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1273
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="n"/>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">17172
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
@@ -2869,143 +2782,145 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3686
+          <t xml:space="preserve">3325
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064
+          <t xml:space="preserve">1672
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">10084
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1894
+</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">1322
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">1580
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">2011
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">467
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">12298
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">1776
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -3024,18 +2939,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>856</t>
+          <t xml:space="preserve">13262
+</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
@@ -3047,122 +2963,121 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-1254
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2929
+          <t xml:space="preserve">1317
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1885
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3181,144 +3096,139 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
+          <t xml:space="preserve">12990
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2415
+          <t xml:space="preserve">1897
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">1197
+</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-1254
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">22384
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">1716
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -3337,143 +3247,142 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">13575
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2128
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">10010
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">1631
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2438
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+          <t xml:space="preserve">1841
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3489,143 +3398,142 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3993
+          <t xml:space="preserve">12949
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">15312
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">2188
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1691
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">1310
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">12165
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3639,149 +3547,82 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7326
-</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422999227
-1149 6
-</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1072
-</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1324
-</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4574532851
-12818
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1070
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1268
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1984
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4940
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">557
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1281
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">893
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12529
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">13200
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1796
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="n"/>
+      <c r="W23" s="3" t="n"/>
+      <c r="X23" s="3" t="n"/>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">4220
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-78
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3800,146 +3641,133 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">575
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1092
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6018
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">1640
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-78
+          <t xml:space="preserve">553
 </t>
         </is>
       </c>
@@ -3958,142 +3786,141 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">067
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24127
-210
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t xml:space="preserve">1229
+</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">779717
-1791818
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7783
-181186
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6541
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -4109,141 +3936,141 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">23450
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>930</t>
+          <t xml:space="preserve">1980
+</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2241
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>844</t>
+          <t xml:space="preserve">552
+</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>621</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+          <t xml:space="preserve">1743
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -4259,144 +4086,141 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">24182
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">2861
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-34
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">042
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1264
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">2955
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1302
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="n"/>
+          <t xml:space="preserve">1742
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1105
+</t>
+        </is>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -4412,143 +4236,142 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
+          <t xml:space="preserve">2823
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">1326
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">12244
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">1226
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">12603
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">1860
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4567,144 +4390,144 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>865</t>
+          <t xml:space="preserve">1202
+</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">368
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2350
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1818
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4721,147 +4544,82 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0566
-</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">315
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4280
+          <t xml:space="preserve">5069
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">966
+          <t xml:space="preserve">1922
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1526
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">14895
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358
-</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1207
-</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="n"/>
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">13445
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="W30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1688
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="n"/>
+      <c r="W30" s="3" t="n"/>
+      <c r="X30" s="3" t="n"/>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">14115
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -4880,145 +4638,138 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112
+          <t xml:space="preserve">2727
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111171
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4826
+          <t xml:space="preserve">1979
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2042
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3968
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">381
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">12067
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417
-</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -5037,144 +4788,139 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3847
+          <t xml:space="preserve">12635
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1290
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1215
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1256
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9901</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">290
 </t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">785
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">439
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">1698
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5193,143 +4939,135 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2423
+          <t xml:space="preserve">1441
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">11290
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2241
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1252
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1834
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1918
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1600
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">610
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2862 2
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5348,146 +5086,140 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
+          <t xml:space="preserve">11178
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-214
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">11678
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1625
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5506,145 +5238,138 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3534
+          <t xml:space="preserve">12844
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">2095
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">060
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1690
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n"/>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
-</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">2754
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5663,144 +5388,146 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4307
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">725
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1690
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">975
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t xml:space="preserve">948
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5818,146 +5545,85 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6937
-</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1287
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8264
+</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">534
+          <t xml:space="preserve">1429
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">427
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3" t="n"/>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">537
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1262
-</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">792798
-11811
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1331
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="n"/>
+      <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3248
+          <t xml:space="preserve">3936
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">466
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="n"/>
+      <c r="W37" s="3" t="n"/>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
+          <t xml:space="preserve">14160
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82745857727
-12119
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5976,145 +5642,135 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387
+          <t xml:space="preserve">1633
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1686
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3607
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431
+          <t xml:space="preserve">19273
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">28111
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">1225
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
+          <t xml:space="preserve">18392
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6133,141 +5789,145 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">3325
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">1907
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>901</t>
+          <t xml:space="preserve">1693
+</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">935
+</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>840</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-111
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t xml:space="preserve">226
+</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">11307
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
+          <t xml:space="preserve">1665
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">729
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1061
 </t>
         </is>
       </c>
@@ -6286,147 +5946,144 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7924
-265
+          <t xml:space="preserve">2781
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3192
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">12297
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-111
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1654
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6445,145 +6102,144 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7924
-265
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1938
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">2093
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">7205
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">1271
+</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">18411
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -6602,145 +6258,145 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2363
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">11886
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">2912
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">16000
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1309
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12071
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">12393
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">1818
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6759,144 +6415,139 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">23116
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1249
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1217
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1240
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">21
 </t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>3546</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">756
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8235
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>354</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">1843
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -6913,150 +6564,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3659
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1060
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">668
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">621
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">462
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">841
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
+      <c r="O44" s="3" t="n"/>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
+      <c r="R44" s="3" t="n"/>
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n"/>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="n"/>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
+      <c r="Y44" s="3" t="n"/>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -7072,91 +6603,60 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">021
-</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">561
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17227
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>061</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">2936
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1649
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7283
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7263
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">987
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">510
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">1918
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
@@ -7164,41 +6664,31 @@
       <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500
+          <t xml:space="preserve">3414
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3581
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1725
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16680
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="n"/>
+      <c r="W45" s="3" t="n"/>
+      <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">9923
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1985
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -7214,143 +6704,141 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">2907
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7283
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">411
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1984
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">12922
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -757,43 +757,43 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">2764
 </t>
         </is>
       </c>
@@ -805,7 +805,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -817,31 +817,31 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112811
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -853,22 +853,17 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1743
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17543
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -890,7 +885,8 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">311
+</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -901,7 +897,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -919,13 +915,13 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -937,36 +933,37 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">0 4
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -978,25 +975,25 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -1014,7 +1011,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -1039,13 +1036,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123680
+          <t xml:space="preserve">2681
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -1057,13 +1054,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12063
+          <t xml:space="preserve">2635
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1075,62 +1072,68 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1251
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">3124
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">273
+</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1141,7 +1144,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
@@ -1153,25 +1156,25 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">454
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1208,7 +1211,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -1220,24 +1223,25 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10113
+          <t xml:space="preserve">011
 </t>
         </is>
       </c>
@@ -1255,30 +1259,31 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19808
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13119
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -1290,13 +1295,13 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595
+          <t xml:space="preserve">595
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
@@ -1308,7 +1313,7 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1345,94 +1350,94 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193680
+          <t xml:space="preserve">96811
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">335
+</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">333
 </t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1275
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1221
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2417
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1965
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1019
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2333
-</t>
-        </is>
-      </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
@@ -1441,19 +1446,19 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -1471,7 +1476,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
@@ -1502,24 +1507,49 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171836
-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
+          <t xml:space="preserve">11850
+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1617
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1074
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13549
+</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121008
+</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -1529,9 +1559,24 @@
 </t>
         </is>
       </c>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1094
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11080
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4870
@@ -1544,37 +1589,57 @@
 </t>
         </is>
       </c>
-      <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="3" t="n"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1566
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1244
+</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13715
+          <t xml:space="preserve">1537905
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9080
+          <t xml:space="preserve">3080
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901
-</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 2 20
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14200
+</t>
+        </is>
+      </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10325
+          <t xml:space="preserve">11395
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13891
+          <t xml:space="preserve">5891
 </t>
         </is>
       </c>
@@ -1599,13 +1664,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23567
+          <t xml:space="preserve">3567
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">8295
 </t>
         </is>
       </c>
@@ -1617,7 +1682,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -1629,23 +1694,23 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">42
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -1666,7 +1731,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -1678,19 +1743,19 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -1702,7 +1767,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -1714,7 +1779,7 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -1726,7 +1791,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">14178
 </t>
         </is>
       </c>
@@ -1751,36 +1816,37 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t xml:space="preserve">420
+</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3933
+          <t xml:space="preserve">9353
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
@@ -1792,19 +1858,19 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">10104
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2016
 </t>
         </is>
       </c>
@@ -1822,13 +1888,13 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -1846,7 +1912,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -1858,19 +1924,19 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26551
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -1882,7 +1948,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -1907,94 +1973,94 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418240
+          <t xml:space="preserve">12182
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">828
+</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">328
 </t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1204
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2201
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12203
-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -2009,19 +2075,19 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19580
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
@@ -2039,13 +2105,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7132
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
@@ -2064,13 +2130,13 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12301
+          <t xml:space="preserve">2301
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -2082,7 +2148,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2094,7 +2160,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2106,74 +2172,79 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -2191,13 +2262,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">8008
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -2216,7 +2287,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18214
+          <t xml:space="preserve">8214
 </t>
         </is>
       </c>
@@ -2228,7 +2299,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2240,36 +2311,37 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2281,31 +2353,31 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">0 4
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2323,7 +2395,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -2341,19 +2413,19 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2378,25 +2450,25 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -2408,18 +2480,19 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>945</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">4080
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10080
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -2431,19 +2504,19 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -2455,7 +2528,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2467,7 +2540,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2479,38 +2552,37 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">7166
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2526,12 +2598,21 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153081
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15242
+</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2542,19 +2623,19 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1545
+          <t xml:space="preserve">5245
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -2566,22 +2647,37 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
+          <t xml:space="preserve">1624
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11290
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14900
+          <t xml:space="preserve">4900
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2591,32 +2687,57 @@
 </t>
         </is>
       </c>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1257
+</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1427
+</t>
+        </is>
+      </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13310
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1763
-</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4126
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2512
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1400
+</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13861
+          <t xml:space="preserve">138611
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">423
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2653,13 +2774,13 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -2671,7 +2792,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2681,7 +2802,12 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="n"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">206
@@ -2696,8 +2822,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2708,25 +2833,25 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">9305
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -2738,32 +2863,37 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="n"/>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17172
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2782,103 +2912,100 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
-</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1192
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11714
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1697
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">322
 </t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1257
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1672
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10084
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1894
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1322
-</t>
-        </is>
-      </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -2890,13 +3017,13 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -2908,19 +3035,19 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12298
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1776
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2939,19 +3066,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13262
+          <t xml:space="preserve">3262
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -2969,7 +3096,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -2981,37 +3108,37 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -3029,25 +3156,25 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">2553
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -3065,13 +3192,13 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -3096,18 +3223,19 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12990
+          <t xml:space="preserve">28990
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>911</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -3125,25 +3253,25 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3155,32 +3283,37 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22384
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3192,7 +3325,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
@@ -3216,13 +3349,13 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
@@ -3247,7 +3380,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13575
+          <t xml:space="preserve">3575
 </t>
         </is>
       </c>
@@ -3259,37 +3392,43 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="n"/>
+          <t xml:space="preserve">18281
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3301,37 +3440,37 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10010
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">0 0
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3343,7 +3482,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
@@ -3361,7 +3500,7 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3373,13 +3512,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">184841
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
@@ -3398,55 +3537,61 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12949
+          <t xml:space="preserve">9929
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15312
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -3464,19 +3609,19 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">108000
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3494,7 +3639,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
@@ -3506,19 +3651,19 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12165
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3547,20 +3692,39 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16101
+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1554
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3575,45 +3739,90 @@
 </t>
         </is>
       </c>
-      <c r="K23" s="3" t="n"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 78
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16133
+</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4940
 </t>
         </is>
       </c>
-      <c r="P23" s="3" t="n"/>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12529
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="n"/>
-      <c r="S23" s="3" t="n"/>
+          <t xml:space="preserve">1529
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12406
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1153947
+</t>
+        </is>
+      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13200
+          <t xml:space="preserve">3200
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1796
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="3" t="n"/>
+          <t xml:space="preserve">796 1
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1406
+</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4220
@@ -3622,7 +3831,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -3641,19 +3850,18 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
+          <t xml:space="preserve">9311
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1092
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
@@ -3677,15 +3885,20 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -3697,41 +3910,43 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">227
+</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">053
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
@@ -3749,26 +3964,25 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">553
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3786,7 +4000,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
@@ -3804,22 +4018,28 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">23
@@ -3828,7 +4048,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3840,24 +4060,25 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3875,7 +4096,7 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3887,37 +4108,37 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">9 52
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3936,24 +4157,25 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23450
+          <t xml:space="preserve">8450
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">9317
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3965,11 +4187,16 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n"/>
+          <t xml:space="preserve">18868
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">144
@@ -3978,7 +4205,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4002,7 +4229,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -4014,19 +4241,19 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">3854
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4044,24 +4271,25 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>621</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1743
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -4086,7 +4314,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24182
+          <t xml:space="preserve">14182
 </t>
         </is>
       </c>
@@ -4098,36 +4326,43 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1387
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n"/>
+          <t xml:space="preserve">1176
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t xml:space="preserve">52
+</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4145,19 +4380,19 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">042
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -4169,19 +4404,19 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
@@ -4199,25 +4434,25 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2955
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1742
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -4248,7 +4483,8 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4265,13 +4501,13 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4283,7 +4519,8 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t xml:space="preserve">800
+</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4294,18 +4531,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -4317,7 +4555,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">29798
 </t>
         </is>
       </c>
@@ -4329,37 +4567,37 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12603
+          <t xml:space="preserve">26595
 </t>
         </is>
       </c>
@@ -4371,8 +4609,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4390,7 +4627,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">1221121
 </t>
         </is>
       </c>
@@ -4408,7 +4645,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">2472
 </t>
         </is>
       </c>
@@ -4426,7 +4663,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4436,12 +4673,7 @@
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
+      <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -4450,30 +4682,31 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">241 9
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -4491,25 +4724,25 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">2515
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2350
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4521,13 +4754,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4544,31 +4777,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6251
+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">565
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11200
+</t>
+        </is>
+      </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069
+          <t xml:space="preserve">5698
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
@@ -4578,42 +4831,87 @@
 </t>
         </is>
       </c>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1802
+</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14895
+          <t xml:space="preserve">4895
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="n"/>
-      <c r="R30" s="3" t="n"/>
-      <c r="S30" s="3" t="n"/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3121
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01 35
+</t>
+        </is>
+      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13445
+          <t xml:space="preserve">3445
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
-</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="n"/>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="n"/>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1274
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1153
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14115
+          <t xml:space="preserve">4115
 </t>
         </is>
       </c>
@@ -4644,7 +4942,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">212461
 </t>
         </is>
       </c>
@@ -4656,25 +4954,25 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4687,89 +4985,91 @@
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1979
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2042
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12067
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t xml:space="preserve">1823
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16828
 </t>
         </is>
       </c>
@@ -4788,13 +5088,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12635
+          <t xml:space="preserve">2635
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -4806,7 +5106,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -4824,11 +5124,16 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">34
@@ -4843,19 +5148,20 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t xml:space="preserve">990
+</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4872,19 +5178,19 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
@@ -4896,31 +5202,31 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4939,7 +5245,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -4963,13 +5269,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4979,10 +5285,14 @@
 </t>
         </is>
       </c>
-      <c r="J33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -5000,7 +5310,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -5010,7 +5320,12 @@
 </t>
         </is>
       </c>
-      <c r="P33" s="3" t="n"/>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
@@ -5025,49 +5340,49 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -5086,7 +5401,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11178
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -5098,13 +5413,13 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">24 9
 </t>
         </is>
       </c>
@@ -5116,7 +5431,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11678
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -5153,25 +5468,25 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -5183,25 +5498,25 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -5213,13 +5528,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5238,25 +5553,25 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12844
+          <t xml:space="preserve">2844
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2095
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -5274,12 +5589,13 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5291,19 +5607,25 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n"/>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t xml:space="preserve">2189
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -5321,19 +5643,19 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2754
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
@@ -5357,7 +5679,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">129593
 </t>
         </is>
       </c>
@@ -5369,7 +5691,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1649
 </t>
         </is>
       </c>
@@ -5412,13 +5734,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5436,7 +5758,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -5454,19 +5776,19 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -5490,31 +5812,31 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -5526,7 +5848,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -5549,12 +5871,27 @@
 </t>
         </is>
       </c>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1429
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11215
+</t>
+        </is>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
@@ -5566,11 +5903,16 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="n"/>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1179
@@ -5583,23 +5925,48 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
-      <c r="O37" s="3" t="n"/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="n"/>
-      <c r="S37" s="3" t="n"/>
+          <t xml:space="preserve">2331
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1363
+</t>
+        </is>
+      </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3936
@@ -5608,16 +5975,31 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="n"/>
-      <c r="W37" s="3" t="n"/>
-      <c r="X37" s="3" t="n"/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1298
+</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14160
+          <t xml:space="preserve">124660
 </t>
         </is>
       </c>
@@ -5642,7 +6024,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1633
+          <t xml:space="preserve">1553
 </t>
         </is>
       </c>
@@ -5654,7 +6036,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2 0 0
 </t>
         </is>
       </c>
@@ -5672,18 +6054,28 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1686
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 1
+</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5692,7 +6084,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5704,7 +6096,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5716,7 +6108,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -5728,31 +6120,31 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">8287
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28111
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -5764,7 +6156,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18392
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
@@ -5789,19 +6181,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">3320
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1693
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -5819,7 +6211,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -5831,13 +6223,13 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5861,19 +6253,19 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11307
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -5891,7 +6283,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">66853
 </t>
         </is>
       </c>
@@ -5903,7 +6295,7 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">2 78
 </t>
         </is>
       </c>
@@ -5915,7 +6307,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">2178
 </t>
         </is>
       </c>
@@ -5927,7 +6319,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1061
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -5946,7 +6338,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">2788
 </t>
         </is>
       </c>
@@ -5964,19 +6356,19 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12297
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -5988,13 +6380,13 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6006,12 +6398,13 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6023,19 +6416,19 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
+          <t xml:space="preserve">807
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -6047,19 +6440,19 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
+          <t xml:space="preserve">654
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -6071,7 +6464,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -6083,7 +6476,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">18114
 </t>
         </is>
       </c>
@@ -6102,7 +6495,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">2486
 </t>
         </is>
       </c>
@@ -6114,7 +6507,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -6126,7 +6519,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6138,7 +6531,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -6150,19 +6543,19 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -6174,7 +6567,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1938
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -6186,7 +6579,7 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
@@ -6198,51 +6591,47 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18411
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1811
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="n"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6288,25 +6677,25 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11886
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6318,7 +6707,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2912
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -6330,49 +6719,49 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1309
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12071
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -6384,7 +6773,7 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12393
+          <t xml:space="preserve">189535
 </t>
         </is>
       </c>
@@ -6415,7 +6804,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23116
+          <t xml:space="preserve">3126
 </t>
         </is>
       </c>
@@ -6427,7 +6816,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
@@ -6449,7 +6838,12 @@
 </t>
         </is>
       </c>
-      <c r="I43" s="3" t="n"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1416
+</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -6470,49 +6864,49 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -6524,7 +6918,7 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -6536,18 +6930,18 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>958</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1843
+          <t xml:space="preserve">18495
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -6564,7 +6958,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -6603,27 +7002,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17227
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
+          <t xml:space="preserve">14234
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9227
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101011
+</t>
+        </is>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>061</t>
+          <t xml:space="preserve">121010
+</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2936
+          <t xml:space="preserve">936
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">025
 </t>
         </is>
       </c>
@@ -6635,33 +7049,53 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="n"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1009001604
+</t>
+        </is>
+      </c>
       <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161285
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">49160
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
+          <t xml:space="preserve">12463
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3414
@@ -6670,22 +7104,36 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16680
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
+          <t xml:space="preserve">66 8
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2220
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14124
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1225
+</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9923
-</t>
+          <t>39831</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">108209
 </t>
         </is>
       </c>
@@ -6710,13 +7158,14 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">1305
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -6727,115 +7176,121 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 5
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2717
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1152
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1268
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2738
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1285
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1206
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1293
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>6451</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1277
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1683
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12922
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1238
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -793,7 +793,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2764
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -805,8 +805,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>061</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -823,7 +822,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -853,13 +852,13 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">2921
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17543
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -915,13 +914,13 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -939,7 +938,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
@@ -981,7 +980,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -1005,7 +1004,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -1036,13 +1035,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -1054,13 +1053,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -1078,7 +1077,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1108,7 +1107,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">9720
 </t>
         </is>
       </c>
@@ -1120,7 +1119,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -1144,7 +1143,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1168,13 +1167,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">454
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1193,7 +1192,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">82182
 </t>
         </is>
       </c>
@@ -1211,7 +1210,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -1223,25 +1222,25 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -1301,7 +1300,7 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -1350,13 +1349,13 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96811
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
@@ -1374,7 +1373,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1386,7 +1385,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1398,7 +1397,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1422,7 +1421,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
@@ -1452,7 +1451,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
@@ -1488,7 +1487,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1507,7 +1506,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11850
+          <t xml:space="preserve">17830
 </t>
         </is>
       </c>
@@ -1525,7 +1524,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13549
+          <t xml:space="preserve">1345
 </t>
         </is>
       </c>
@@ -1537,7 +1536,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121008
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
@@ -1567,13 +1566,13 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11080
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1591,7 +1590,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">85566
 </t>
         </is>
       </c>
@@ -1603,7 +1602,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537905
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
@@ -1621,25 +1620,25 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 2 20
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11395
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891
+          <t xml:space="preserve">3891
 </t>
         </is>
       </c>
@@ -1664,13 +1663,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
+          <t xml:space="preserve">2567
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1694,11 +1693,16 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">42
@@ -1707,13 +1711,13 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -1761,7 +1765,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">6 1 6
 </t>
         </is>
       </c>
@@ -1779,19 +1783,19 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14178
+          <t xml:space="preserve">8778
 </t>
         </is>
       </c>
@@ -1822,13 +1826,13 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9353
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1892
 </t>
         </is>
       </c>
@@ -1840,37 +1844,37 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10104
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -1918,7 +1922,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1563
+          <t xml:space="preserve">2563
 </t>
         </is>
       </c>
@@ -1954,7 +1958,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -1979,7 +1983,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -2009,13 +2013,13 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2039,7 +2043,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2063,7 +2067,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25 8
 </t>
         </is>
       </c>
@@ -2075,7 +2079,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -2099,19 +2103,19 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1303
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">7132
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -2130,7 +2134,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
+          <t xml:space="preserve">2381
 </t>
         </is>
       </c>
@@ -2166,7 +2170,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2208,7 +2212,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2256,13 +2260,13 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8008
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -2287,7 +2291,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8214
+          <t xml:space="preserve">12214
 </t>
         </is>
       </c>
@@ -2335,7 +2339,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2419,13 +2423,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -2456,52 +2460,52 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">195
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4080
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -2528,22 +2532,22 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">8300
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">300
 </t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">710
@@ -2552,13 +2556,13 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
@@ -2576,7 +2580,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7166
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
@@ -2606,7 +2610,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15242
+          <t xml:space="preserve">1542
 </t>
         </is>
       </c>
@@ -2617,25 +2621,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2647,25 +2650,25 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1624
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -2689,13 +2692,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2707,19 +2710,19 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2512
+          <t xml:space="preserve">2120
 </t>
         </is>
       </c>
@@ -2731,13 +2734,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138611
+          <t xml:space="preserve">3861
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -2762,8 +2765,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2774,7 +2776,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2804,7 +2806,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -2822,24 +2824,24 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>38886</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -2857,13 +2859,13 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
+          <t xml:space="preserve">19662
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -2881,13 +2883,13 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">7722
 </t>
         </is>
       </c>
@@ -2917,12 +2919,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>324</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2940,13 +2942,13 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11714
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2963,13 +2965,13 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -3011,7 +3013,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -3035,7 +3037,7 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -3047,8 +3049,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3096,7 +3097,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3132,7 +3133,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -3150,13 +3151,13 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2553
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -3174,19 +3175,19 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3223,7 +3224,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28990
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
@@ -3241,7 +3242,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -3253,7 +3254,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -3337,13 +3338,13 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3392,7 +3393,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3404,25 +3405,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18281
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3452,13 +3453,13 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">8000
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 0
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3506,19 +3507,19 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184841
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -3537,13 +3538,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9929
-</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -3561,13 +3561,13 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
@@ -3609,19 +3609,19 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
@@ -3706,25 +3706,25 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">2258
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -3753,13 +3753,13 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 78
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16133
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3783,13 +3783,13 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12406
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153947
+          <t xml:space="preserve">11397
 </t>
         </is>
       </c>
@@ -3801,26 +3801,25 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796 1
+          <t xml:space="preserve">795 1
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3831,7 +3830,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3850,12 +3849,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9311
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -3885,17 +3884,17 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1019
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">197
@@ -3904,7 +3903,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -3922,67 +3921,68 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">844
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">053
 </t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">640
-</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4036,8 +4036,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -4054,14 +4053,12 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>41104</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -4120,7 +4117,7 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -4157,13 +4154,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8450
+          <t xml:space="preserve">23450
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9317
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
@@ -4187,13 +4184,13 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18868
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4205,7 +4202,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4223,8 +4220,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -4233,15 +4229,10 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+      <c r="P26" s="3" t="n"/>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3854
+          <t xml:space="preserve">884
 </t>
         </is>
       </c>
@@ -4314,13 +4305,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14182
+          <t xml:space="preserve">4182
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -4338,7 +4329,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1387
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4350,7 +4341,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -4380,7 +4371,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -4434,13 +4425,12 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">8082
 </t>
         </is>
       </c>
@@ -4477,7 +4467,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">3256
 </t>
         </is>
       </c>
@@ -4501,7 +4491,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -4519,7 +4509,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4555,7 +4545,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29798
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -4579,7 +4569,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -4597,13 +4587,13 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26595
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
@@ -4627,8 +4617,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221121
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4645,7 +4634,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2472
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -4669,20 +4658,20 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2189
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241 9
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4712,7 +4701,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4730,7 +4719,7 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515
+          <t xml:space="preserve">1073
 </t>
         </is>
       </c>
@@ -4748,19 +4737,19 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4777,21 +4766,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6251
-</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
-</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4803,49 +4786,48 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
-</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9228
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
@@ -4857,25 +4839,25 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">755
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01 35
+          <t xml:space="preserve">18 35
 </t>
         </is>
       </c>
@@ -4942,7 +4924,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212461
+          <t xml:space="preserve">513
 </t>
         </is>
       </c>
@@ -4954,19 +4936,14 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n"/>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -4991,7 +4968,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">20 2
 </t>
         </is>
       </c>
@@ -5039,19 +5016,19 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -5063,13 +5040,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16828
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -5118,7 +5095,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -5130,7 +5107,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5214,19 +5191,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -5245,7 +5222,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
@@ -5257,57 +5234,58 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2006
+</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1225
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">206
 </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
@@ -5346,7 +5324,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
@@ -5382,7 +5360,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5413,7 +5391,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -5441,7 +5419,11 @@
 </t>
         </is>
       </c>
-      <c r="J34" s="3" t="n"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">59
@@ -5474,7 +5456,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5498,13 +5480,13 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5516,7 +5498,7 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -5528,13 +5510,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5607,7 +5589,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5619,7 +5601,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">2149
 </t>
         </is>
       </c>
@@ -5655,7 +5637,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5679,7 +5661,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129593
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
@@ -5691,7 +5673,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5710,7 +5692,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -5734,7 +5716,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5752,7 +5734,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5788,7 +5770,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -5816,12 +5798,7 @@
 </t>
         </is>
       </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+      <c r="U36" s="3" t="n"/>
       <c r="V36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -5830,8 +5807,7 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -5848,7 +5824,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -5879,13 +5855,13 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
@@ -5909,103 +5885,103 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18079
+</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0229
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 0
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1338
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39236
+</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1179
-</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1034
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2331
-</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1272
-</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1363
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3936
-</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1241
-</t>
-        </is>
-      </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1298
-</t>
-        </is>
-      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124660
+          <t xml:space="preserve">4160
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -6024,7 +6000,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
+          <t xml:space="preserve">1653
 </t>
         </is>
       </c>
@@ -6054,7 +6030,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18 6
 </t>
         </is>
       </c>
@@ -6066,13 +6042,13 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">2 8
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6084,7 +6060,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -6108,7 +6084,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">2566
 </t>
         </is>
       </c>
@@ -6120,13 +6096,12 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>485</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8287
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
@@ -6138,7 +6113,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -6150,13 +6125,13 @@
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
@@ -6181,7 +6156,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -6211,19 +6186,19 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -6259,7 +6234,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
@@ -6283,7 +6258,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66853
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
@@ -6307,7 +6282,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -6338,13 +6313,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2788
+          <t xml:space="preserve">27281
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -6368,7 +6343,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -6380,7 +6355,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -6404,7 +6379,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
@@ -6422,13 +6397,13 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6446,7 +6421,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -6476,7 +6451,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18114
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6495,7 +6470,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2486
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
@@ -6543,7 +6518,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -6579,13 +6554,13 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -6597,7 +6572,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6627,11 +6602,16 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="n"/>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6677,7 +6657,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -6689,7 +6669,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6707,7 +6687,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
@@ -6725,7 +6705,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -6773,13 +6753,13 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189535
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -6804,26 +6784,25 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126
+          <t xml:space="preserve">3116
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -6834,13 +6813,13 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6882,7 +6861,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6930,12 +6909,12 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>854</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18495
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
@@ -7008,24 +6987,25 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>705</t>
+          <t xml:space="preserve">1027
+</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101011
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121010
+          <t xml:space="preserve">1906
 </t>
         </is>
       </c>
@@ -7037,57 +7017,56 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">025
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">18149
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009001604
+          <t xml:space="preserve">1050816
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161285
+          <t xml:space="preserve">18205
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49160
+          <t xml:space="preserve">4918
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">16 9
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12463
+          <t xml:space="preserve">8463
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>633</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -7110,30 +7089,31 @@
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14124
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t xml:space="preserve">99295
+</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108209
+          <t xml:space="preserve">0805
 </t>
         </is>
       </c>
@@ -7158,7 +7138,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -7176,13 +7156,13 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1091
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
@@ -7200,7 +7180,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 5
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -7212,7 +7192,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -7236,7 +7216,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
@@ -7248,7 +7228,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2717
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -7260,37 +7240,37 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2738
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
@@ -734,7 +734,8 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>336</t>
+          <t xml:space="preserve">335
+</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -769,7 +770,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -793,7 +794,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -805,12 +806,13 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>061</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1330
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
@@ -822,7 +824,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -852,7 +854,7 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2921
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -862,7 +864,12 @@
 </t>
         </is>
       </c>
-      <c r="Z4" s="3" t="n"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -938,7 +945,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -956,7 +963,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 4
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -980,13 +987,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -1010,13 +1017,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1920
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1035,7 +1042,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">23680
 </t>
         </is>
       </c>
@@ -1059,7 +1066,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1077,7 +1084,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1107,13 +1114,13 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -1137,7 +1144,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">596
 </t>
         </is>
       </c>
@@ -1173,7 +1180,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1192,7 +1199,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82182
+          <t xml:space="preserve">4182
 </t>
         </is>
       </c>
@@ -1222,7 +1229,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1234,13 +1241,13 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -1258,7 +1265,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -1276,7 +1283,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1318,7 +1325,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -1349,7 +1356,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">23680
 </t>
         </is>
       </c>
@@ -1361,7 +1368,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
@@ -1385,7 +1392,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1421,13 +1428,13 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -1445,19 +1452,19 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
@@ -1475,7 +1482,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1487,7 +1494,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1506,7 +1513,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17830
+          <t xml:space="preserve">17836
 </t>
         </is>
       </c>
@@ -1530,7 +1537,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">543
 </t>
         </is>
       </c>
@@ -1572,7 +1579,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">12 82
 </t>
         </is>
       </c>
@@ -1584,13 +1591,13 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85566
+          <t xml:space="preserve">2556
 </t>
         </is>
       </c>
@@ -1602,7 +1609,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">1375
 </t>
         </is>
       </c>
@@ -1620,7 +1627,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1357
 </t>
         </is>
       </c>
@@ -1632,7 +1639,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1395
 </t>
         </is>
       </c>
@@ -1644,7 +1651,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
@@ -1663,19 +1670,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2567
+          <t xml:space="preserve">3567
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2135
 </t>
         </is>
       </c>
@@ -1693,13 +1700,13 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1711,13 +1718,13 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1741,7 +1748,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -1765,13 +1772,13 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 1 6
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1795,13 +1802,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8778
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1826,49 +1833,48 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1892
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1922,7 +1928,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2563
+          <t xml:space="preserve">563
 </t>
         </is>
       </c>
@@ -1952,13 +1958,13 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">704
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1977,7 +1983,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12182
+          <t xml:space="preserve">24182
 </t>
         </is>
       </c>
@@ -2007,19 +2013,19 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2043,7 +2049,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
@@ -2067,7 +2073,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 8
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2085,7 +2091,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
@@ -2103,13 +2109,13 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">1303
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7132
+          <t xml:space="preserve">1732
 </t>
         </is>
       </c>
@@ -2134,7 +2140,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381
+          <t xml:space="preserve">2301
 </t>
         </is>
       </c>
@@ -2170,7 +2176,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -2200,7 +2206,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -2212,7 +2218,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2272,7 +2278,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2291,7 +2297,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12214
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
@@ -2303,7 +2309,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
@@ -2321,7 +2327,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -2357,7 +2363,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -2369,7 +2375,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 4
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2423,13 +2429,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2448,7 +2454,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">23408
 </t>
         </is>
       </c>
@@ -2490,7 +2496,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -2514,7 +2520,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
@@ -2532,7 +2538,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2562,13 +2568,13 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2419
 </t>
         </is>
       </c>
@@ -2586,7 +2592,8 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">74
+</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2604,7 +2611,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153081
+          <t xml:space="preserve">15308
 </t>
         </is>
       </c>
@@ -2616,12 +2623,14 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>992</t>
+          <t xml:space="preserve">997
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">2268
+</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2632,7 +2641,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">11921
 </t>
         </is>
       </c>
@@ -2656,19 +2665,19 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -2692,13 +2701,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1427
 </t>
         </is>
       </c>
@@ -2710,19 +2719,19 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">763
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1365
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -2740,7 +2749,7 @@
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1423
 </t>
         </is>
       </c>
@@ -2759,13 +2768,14 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3062
+          <t xml:space="preserve">2306
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2776,7 +2786,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
@@ -2806,7 +2816,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2836,7 +2846,8 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -2859,7 +2870,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19662
+          <t xml:space="preserve">1662
 </t>
         </is>
       </c>
@@ -2889,13 +2900,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7722
+          <t xml:space="preserve">772
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -2914,12 +2925,14 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">322
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2930,30 +2943,31 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2971,13 +2985,13 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -2989,7 +3003,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -3019,7 +3033,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
@@ -3049,7 +3063,8 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3067,13 +3082,13 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">1322
 </t>
         </is>
       </c>
@@ -3133,7 +3148,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
@@ -3193,7 +3208,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -3230,7 +3245,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
@@ -3248,13 +3263,13 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">11184
 </t>
         </is>
       </c>
@@ -3278,19 +3293,19 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">11197
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -3381,7 +3396,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3575
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
@@ -3393,7 +3408,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -3411,7 +3426,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
@@ -3441,19 +3456,19 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000
+          <t xml:space="preserve">16000
 </t>
         </is>
       </c>
@@ -3513,7 +3528,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">18441
 </t>
         </is>
       </c>
@@ -3538,7 +3553,8 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t xml:space="preserve">2949
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3549,13 +3565,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">12380
 </t>
         </is>
       </c>
@@ -3567,7 +3583,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">11674
 </t>
         </is>
       </c>
@@ -3591,7 +3607,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -3603,7 +3619,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
@@ -3615,13 +3631,13 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3639,13 +3655,13 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -3657,7 +3673,7 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -3669,7 +3685,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -3694,7 +3710,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16101
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
@@ -3706,13 +3722,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">0962
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -3724,7 +3740,8 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">882
+</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3759,7 +3776,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
@@ -3789,7 +3806,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -3801,25 +3818,26 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">795 1
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t xml:space="preserve">1406
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3830,7 +3848,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -3849,7 +3867,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t xml:space="preserve">3220
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3860,7 +3879,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3888,10 +3907,15 @@
 </t>
         </is>
       </c>
-      <c r="J24" s="3" t="n"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3903,7 +3927,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -3915,7 +3939,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -3945,7 +3969,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">1640
 </t>
         </is>
       </c>
@@ -3957,7 +3981,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4036,7 +4060,8 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -4053,12 +4078,13 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -4117,7 +4143,7 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -4129,7 +4155,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 52
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
@@ -4196,7 +4222,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -4220,7 +4246,8 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -4229,10 +4256,15 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="3" t="n"/>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -4244,7 +4276,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -4329,7 +4361,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -4341,7 +4373,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -4371,7 +4403,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4425,12 +4457,13 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8082
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -4461,13 +4494,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2823
+          <t xml:space="preserve">2824
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3256
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
@@ -4479,7 +4512,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">2682
 </t>
         </is>
       </c>
@@ -4491,7 +4524,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -4515,7 +4548,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
@@ -4581,13 +4614,13 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
@@ -4599,7 +4632,8 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">143
+</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4617,7 +4651,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4662,10 +4696,15 @@
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="n"/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4701,7 +4740,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
@@ -4719,7 +4758,7 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1073
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4749,7 +4788,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4766,10 +4805,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1363
+</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t xml:space="preserve">11565
+</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4780,30 +4825,31 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11200
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t xml:space="preserve">2569
+</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9228
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">11718
 </t>
         </is>
       </c>
@@ -4815,19 +4861,19 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1011
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -4845,19 +4891,19 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">1455
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4887,13 +4933,13 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1337
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115
+          <t xml:space="preserve">24115
 </t>
         </is>
       </c>
@@ -4924,7 +4970,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">513
+          <t xml:space="preserve">1313
 </t>
         </is>
       </c>
@@ -4940,7 +4986,12 @@
 </t>
         </is>
       </c>
-      <c r="G31" s="3" t="n"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
@@ -4955,11 +5006,16 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -4968,7 +5024,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 2
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -4980,7 +5036,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5016,19 +5072,19 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">11138
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
@@ -5046,7 +5102,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -5071,88 +5127,87 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1290
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1215
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">290
 </t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -5161,7 +5216,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
@@ -5185,25 +5240,25 @@
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5222,7 +5277,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
@@ -5234,7 +5289,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -5258,19 +5313,19 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5288,7 +5343,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
@@ -5324,7 +5379,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -5358,12 +5413,7 @@
 </t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+      <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -5397,7 +5447,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 9
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -5421,7 +5471,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -5432,19 +5482,19 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1201
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">201
 </t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -5601,7 +5651,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2149
+          <t xml:space="preserve">2139
 </t>
         </is>
       </c>
@@ -5613,7 +5663,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5661,13 +5711,13 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">2093
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">1858
 </t>
         </is>
       </c>
@@ -5692,13 +5742,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -5716,13 +5766,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">11190
 </t>
         </is>
       </c>
@@ -5740,7 +5790,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5758,7 +5808,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -5798,7 +5848,12 @@
 </t>
         </is>
       </c>
-      <c r="U36" s="3" t="n"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -5807,7 +5862,8 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>618</t>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -5818,13 +5874,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5855,19 +5911,19 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">1429
 </t>
         </is>
       </c>
@@ -5885,13 +5941,13 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18079
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -5903,49 +5959,49 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0229
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">4950
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 0
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1338
+          <t xml:space="preserve">1331
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1363
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39236
+          <t xml:space="preserve">3936
 </t>
         </is>
       </c>
@@ -5957,19 +6013,19 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
@@ -6000,7 +6056,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6012,13 +6068,13 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 0 0
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6030,7 +6086,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 6
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -6042,13 +6098,13 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 8
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6060,7 +6116,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6084,7 +6140,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -6096,24 +6152,25 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>485</t>
+          <t xml:space="preserve">273
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">788
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -6131,13 +6188,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -6156,7 +6213,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">3323
 </t>
         </is>
       </c>
@@ -6180,7 +6237,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
@@ -6192,52 +6249,52 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">5 8
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">35
 </t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">002
-</t>
-        </is>
-      </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">307
@@ -6258,19 +6315,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 78
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -6282,19 +6339,19 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">1729
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6313,19 +6370,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27281
+          <t xml:space="preserve">2781
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">12006
 </t>
         </is>
       </c>
@@ -6373,13 +6430,13 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -6415,7 +6472,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">1654
 </t>
         </is>
       </c>
@@ -6433,7 +6490,7 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -6451,7 +6508,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -6476,7 +6533,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
@@ -6506,16 +6563,11 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
@@ -6530,7 +6582,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -6572,7 +6624,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">7205
 </t>
         </is>
       </c>
@@ -6584,7 +6636,7 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
@@ -6596,19 +6648,19 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">8411
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -6687,13 +6739,13 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
@@ -6705,7 +6757,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6747,13 +6799,13 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -6802,24 +6854,25 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">259
+</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1086
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">416
 </t>
         </is>
       </c>
@@ -6849,7 +6902,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
@@ -6861,7 +6914,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6879,28 +6932,28 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1240
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">240
 </t>
         </is>
       </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">770
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
@@ -6909,7 +6962,8 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>854</t>
+          <t xml:space="preserve">1252
+</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -6920,8 +6974,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6987,19 +7040,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">0527
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1027
+          <t xml:space="preserve">8021
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">11278
 </t>
         </is>
       </c>
@@ -7017,13 +7070,13 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -7035,14 +7088,19 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1050816
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n"/>
+          <t xml:space="preserve">1038
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1029
+</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18205
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
@@ -7054,24 +7112,25 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 9
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463
+          <t xml:space="preserve">1463
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>633</t>
+          <t xml:space="preserve">1223
+</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1384
 </t>
         </is>
       </c>
@@ -7083,37 +7142,37 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66 8
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">12340
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">2190
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1381
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99295
+          <t xml:space="preserve">3923
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
@@ -7156,13 +7215,13 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1091
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -7180,7 +7239,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -7192,7 +7251,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -7216,13 +7275,13 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -7258,7 +7317,7 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">2276
 </t>
         </is>
       </c>
@@ -7270,7 +7329,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
@@ -728,146 +728,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3513
-</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -885,146 +861,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
-</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1042,146 +994,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23680
-</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">596
-</t>
+          <t>596</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1199,146 +1127,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1356,146 +1260,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23680
-</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2418
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1513,146 +1393,122 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17836
-</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617
-</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1074
-</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1345
-</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
-</t>
+          <t>543</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
-</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
-</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 82
-</t>
+          <t>12 82</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4870
-</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556
-</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
-</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080
-</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
-</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1395
-</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3891
-</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1670,146 +1526,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
-</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
-</t>
+          <t>616</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1827,8 +1659,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1838,134 +1669,112 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
-</t>
+          <t>563</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
-</t>
+          <t>704</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1983,146 +1792,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2140,146 +1925,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
-</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
-</t>
+          <t>679</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
-</t>
+          <t>808</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2297,146 +2058,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
-</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2454,146 +2191,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23408
-</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2419
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
-</t>
+          <t>766</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2611,146 +2324,122 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15308
-</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1542
-</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
-</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2268
-</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
-</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524
-</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
-</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
-</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">763
-</t>
+          <t>763</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
-</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
-</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
-</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423
-</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2768,146 +2457,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2306
-</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2925,146 +2590,122 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3082,146 +2723,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3239,146 +2856,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
-</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
-</t>
+          <t>716</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3396,146 +2989,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
-</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18441
-</t>
+          <t>841</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3553,146 +3122,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
-</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12380
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11674
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3710,146 +3255,122 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
-</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554
-</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0962
-</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
-</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
-</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
+          <t>796</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
-</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
-</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3867,146 +3388,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">053
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4024,56 +3521,47 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
-</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -4083,86 +3571,72 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4180,146 +3654,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23450
-</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4337,146 +3787,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4494,146 +3920,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2824
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2682
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4656,140 +4058,117 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4807,146 +4186,122 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1363
-</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11565
-</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11718
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
-</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4895
-</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
-</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445
-</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
-</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1337
-</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4964,146 +4319,122 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
-</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>979</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
-</t>
+          <t>823</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5121,14 +4452,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
-</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5138,128 +4467,107 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
-</t>
+          <t>698</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5277,140 +4585,117 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="Z33" s="3" t="n"/>
@@ -5429,44 +4714,37 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -5476,98 +4754,82 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>702</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5585,146 +4847,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844
-</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5742,146 +4980,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11172
-</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5899,146 +5113,122 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
-</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
-</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
-</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
-</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
-</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
-</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1363
-</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3936
-</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
+          <t>404</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
-</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
-</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6056,146 +5246,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">788
-</t>
+          <t>787</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6213,146 +5379,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3323
-</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 8
-</t>
+          <t>0 08</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
-</t>
+          <t>665</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1729
-</t>
+          <t>729</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6370,146 +5512,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
-</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12006
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
-</t>
+          <t>654</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6527,141 +5645,118 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
-</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205
-</t>
+          <t>705</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8411
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6679,146 +5774,122 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
-</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6836,140 +5907,117 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
-</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>843</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
@@ -6992,8 +6040,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -7034,146 +6081,122 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14234
-</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0527
-</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8021
-</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11278
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">936
-</t>
+          <t>936</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
-</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463
-</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384
-</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
-</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12340
-</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
-</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3923
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7191,146 +6214,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
-</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>785</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>422</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>219</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>0 08</t>
+          <t>01 01</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
@@ -1463,7 +1463,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>282</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>01 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>002</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>138</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/203/original_transcribed_data.xlsx
@@ -728,48 +728,49 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3513
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>335</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -781,91 +782,91 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">8118
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -884,144 +885,145 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">4035
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">326
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">254
 </t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">1566
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1040,49 +1042,49 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">4223
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1094,92 +1096,91 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">596
+          <t xml:space="preserve">552
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1197,145 +1198,142 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>43351</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2351
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1354,144 +1352,143 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11190
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">206
 </t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">2409
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t xml:space="preserve">965
+</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1510,140 +1507,143 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17836
+          <t xml:space="preserve">17835
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617
+          <t xml:space="preserve">1648
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t xml:space="preserve">969
+</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">894
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
+          <t xml:space="preserve">1002
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">996
+</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">1158
+</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">18945
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">1496
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1219
+</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">1357
+</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308 10
+          <t xml:space="preserve">2299
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">1328
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">1168
+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3891
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3888
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1665,122 +1665,122 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">8244
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">416
 </t>
         </is>
       </c>
@@ -1811,48 +1811,49 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4203
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">1866
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -1864,90 +1865,91 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">11245
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">0923
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29332
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
+          <t xml:space="preserve">706
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t xml:space="preserve">840
+</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1966,143 +1968,145 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">3471
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">1446
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9233
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t xml:space="preserve">975
+</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">767
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -2121,145 +2125,145 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
+          <t xml:space="preserve">14286
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">966
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">2221
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2278,145 +2282,145 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">1903
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">3207
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="S14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -2435,145 +2439,146 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">3596
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14196
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1800
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">617
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
+          <t xml:space="preserve">731
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2591,141 +2596,133 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>53041</t>
+          <t xml:space="preserve">15912
+</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15242
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
+          <t xml:space="preserve">1055
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1317
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0289
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">019
+          <t xml:space="preserve">1095
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>097</t>
+          <t xml:space="preserve">1307
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
+          <t xml:space="preserve">4901
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524
+          <t xml:space="preserve">1487
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">1219
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1361
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1763
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
+          <t xml:space="preserve">1337
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">1207
+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">1425
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4074
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2741,37 +2738,37 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3062
+          <t xml:space="preserve">3182
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2783,30 +2780,31 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>519</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">368
 </t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -2818,63 +2816,66 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>014</t>
+          <t xml:space="preserve">1104
+</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2722
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">664
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">285
 </t>
         </is>
       </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">668
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -2893,101 +2894,98 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">8267
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">923
+</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">8252
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -2999,36 +2997,37 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">8200
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t xml:space="preserve">717
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3047,19 +3046,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -3071,121 +3070,120 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3203,145 +3201,146 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">3659
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">623
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">716
-</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t>514</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3359,143 +3358,146 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3575
+          <t xml:space="preserve">3408
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
+          <t xml:space="preserve">712
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t xml:space="preserve">278
+</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">7723
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">84
+</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3513,145 +3515,145 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
+          <t xml:space="preserve">3993
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3189
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">8216
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -3670,142 +3672,140 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16101
+          <t xml:space="preserve">17396
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150519
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
-</t>
+          <t>037</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">1324
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">503
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9728
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4940
+          <t xml:space="preserve">14894
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12529
+          <t xml:space="preserve">1557
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19116
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t xml:space="preserve">11468
+</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
+          <t xml:space="preserve">3957
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18993
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t xml:space="preserve">1203
+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
-</t>
+          <t>39404</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -3824,125 +3824,145 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">3439
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">315
+</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1018
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1082
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1070
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1268
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">979
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">311
 </t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11170
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">651
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="n"/>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -3961,122 +3981,144 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">1067
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">235
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n"/>
+          <t xml:space="preserve">979
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="n"/>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21461
+</t>
+        </is>
+      </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>936</t>
+          <t xml:space="preserve">844
+</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">53
+</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -4095,144 +4137,144 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>9240</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12970
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">24
 </t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="V26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">552
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t xml:space="preserve">271
+</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">877
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4251,90 +4293,91 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>329</t>
+          <t xml:space="preserve">305
+</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2861
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -4346,49 +4389,49 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4407,37 +4450,37 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2823
+          <t xml:space="preserve">29907
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4449,7 +4492,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4461,91 +4504,91 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12201
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">244
 </t>
         </is>
       </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -4564,143 +4607,143 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1402
-</t>
+          <t>34681</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1953
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">11
 </t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">8253
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">726
+</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4719,138 +4762,145 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13635
+          <t xml:space="preserve">10562
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15065
+          <t xml:space="preserve">1452
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t xml:space="preserve">032
+</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">1065
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11592
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4895
+          <t xml:space="preserve">4876
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
+          <t xml:space="preserve">11858
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t xml:space="preserve">1207
+</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t xml:space="preserve">1409
+</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445
+          <t xml:space="preserve">3968
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">1261
+</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>531</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4869,140 +4919,144 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
+          <t xml:space="preserve">2112
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">966
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">388
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5021,137 +5075,144 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
+          <t xml:space="preserve">3847
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">8248
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n"/>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t xml:space="preserve">610
+</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
@@ -5170,143 +5231,144 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">2133
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">516
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">10214
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">2846
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">709
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t xml:space="preserve">746
+</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5324,138 +5386,142 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">3116
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">2114
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">8254
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">11990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>21382484</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5473,144 +5539,146 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844
+          <t xml:space="preserve">3534
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>663</t>
+          <t xml:space="preserve">278
+</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2466
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">65
+</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5628,143 +5696,145 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">4307
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2410
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">9725
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">794
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5783,139 +5853,143 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
+          <t xml:space="preserve">16937
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
+          <t xml:space="preserve">1554
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>00401</t>
+          <t xml:space="preserve">1020
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">534
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">101
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>12034446</t>
+          <t xml:space="preserve">1060
+</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>0444</t>
+          <t xml:space="preserve">10159
+</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
+          <t xml:space="preserve">11927
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
+          <t xml:space="preserve">1537
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112879
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3936
+          <t xml:space="preserve">3248
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
+          <t xml:space="preserve">777
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">1368
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">0011
 </t>
         </is>
       </c>
@@ -5934,134 +6008,145 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
+          <t xml:space="preserve">3387
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">356
+</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1281
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">985
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">286
 </t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">650
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="n"/>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">787
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">982
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6086,59 +6171,70 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>5455</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n"/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n"/>
+          <t xml:space="preserve">9209
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2148
+</t>
+        </is>
+      </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">990
@@ -6153,60 +6249,62 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">632
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">386
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6224,49 +6322,49 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">4537
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -6278,25 +6376,26 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">9468
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>988</t>
+          <t xml:space="preserve">978
+</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -6307,60 +6406,61 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">8293
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">705
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">982
+</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6379,144 +6479,144 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">8256
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>434</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">9286
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">8281
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -6535,19 +6635,19 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
+          <t xml:space="preserve">2363
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">1316
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6559,50 +6659,55 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n"/>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9218
+</t>
+        </is>
+      </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
@@ -6614,59 +6719,62 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">977
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">282
+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>843</t>
+          <t xml:space="preserve">906
+</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6684,66 +6792,82 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>77797</t>
+          <t xml:space="preserve">3722
+</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">857
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0196
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n"/>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n"/>
+          <t xml:space="preserve">956
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -6752,41 +6876,60 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">847
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3923
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -6805,87 +6948,145 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>77797</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
+          <t xml:space="preserve">3659
+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">326
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">823
+</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">800
+</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124612
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620
+</t>
+        </is>
+      </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">844
+</t>
+        </is>
+      </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -6904,127 +7105,139 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t xml:space="preserve">19016
+</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1561
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>4274</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18259
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59838
+</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1728
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>9346</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">984
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277
-</t>
-        </is>
-      </c>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">683
-</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1449
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">5037
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -7041,95 +7254,145 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2376
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="n"/>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
+          <t xml:space="preserve">750
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2141
+</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
